--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488199_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488199_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.902100000000001</v>
+        <v>8.981999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3074</v>
+        <v>10.2642</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4053</v>
+        <v>-1.2822</v>
       </c>
       <c r="G2" t="n">
         <v>9.415900000000001</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4402</v>
+        <v>-0.3603</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4551</v>
+        <v>0.4119</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8954</v>
+        <v>-0.7723</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6294</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4235</v>
+        <v>7.139</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6368</v>
+        <v>5.7463</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7867</v>
+        <v>1.3928</v>
       </c>
       <c r="G3" t="n">
         <v>5.2069</v>
@@ -688,13 +688,13 @@
         <v>2.594</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2335</v>
+        <v>-0.051</v>
       </c>
       <c r="T3" t="n">
-        <v>0.342</v>
+        <v>0.4514</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1085</v>
+        <v>-0.5024</v>
       </c>
       <c r="V3" t="n">
         <v>0.3155</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5907</v>
+        <v>3.9268</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2267</v>
+        <v>2.1195</v>
       </c>
       <c r="F4" t="n">
-        <v>1.364</v>
+        <v>1.8072</v>
       </c>
       <c r="G4" t="n">
         <v>2.068</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.831</v>
+        <v>-0.4949</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8754</v>
+        <v>0.0174</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9555</v>
+        <v>-0.5124</v>
       </c>
       <c r="V4" t="n">
         <v>0.3155</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3379</v>
+        <v>1.5662</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1913</v>
+        <v>1.5662</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1466</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7008</v>
+        <v>1.5662</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6708</v>
+        <v>0.3221</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3717</v>
+        <v>1.2441</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0485</v>
+        <v>1.5662</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.108</v>
+        <v>0.3221</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1565</v>
+        <v>1.2441</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3477</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5628</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2152</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1368</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6813</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5444</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2004</v>
+        <v>1.438</v>
       </c>
       <c r="E6" t="n">
-        <v>5.4746</v>
+        <v>1.2668</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.2743</v>
+        <v>0.1712</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5836</v>
+        <v>1.7008</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8482</v>
+        <v>-0.6708</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7354000000000001</v>
+        <v>2.3717</v>
       </c>
       <c r="J6" t="n">
-        <v>5.083</v>
+        <v>2.0485</v>
       </c>
       <c r="K6" t="n">
-        <v>4.148</v>
+        <v>-0.108</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9350000000000001</v>
+        <v>2.1565</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4994</v>
+        <v>-0.3477</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2998</v>
+        <v>-0.5628</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1996</v>
+        <v>0.2152</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7793</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.6322</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0811</v>
+        <v>0.2369</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2473</v>
+        <v>0.7567</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1662</v>
+        <v>-0.5198</v>
       </c>
       <c r="V6" t="n">
-        <v>0.315</v>
+        <v>-0.3144</v>
       </c>
       <c r="W6" t="n">
-        <v>3.7766</v>
+        <v>0.3144</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.4616</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5662</v>
+        <v>1.268</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5662</v>
+        <v>5.0155</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-3.7475</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5662</v>
+        <v>4.3428</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3221</v>
+        <v>-0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2441</v>
+        <v>4.3898</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5662</v>
+        <v>5.9121</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3221</v>
+        <v>1.2151</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2441</v>
+        <v>4.6969</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-1.5693</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.2621</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.3071</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.5571</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.0299</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.587</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8517</v>
+        <v>1.2243</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6238</v>
+        <v>4.9418</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.7721</v>
+        <v>-3.7174</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3428</v>
+        <v>3.5836</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.047</v>
+        <v>2.8482</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3898</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>5.9121</v>
+        <v>5.083</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2151</v>
+        <v>4.148</v>
       </c>
       <c r="L8" t="n">
-        <v>4.6969</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5693</v>
+        <v>-1.4994</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2621</v>
+        <v>-1.2998</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3071</v>
+        <v>-0.1996</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-4.6322</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9734</v>
+        <v>0.1051</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3619</v>
+        <v>0.7144</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6116</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5177</v>
+        <v>0.315</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.7766</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.5177</v>
+        <v>-3.4616</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0218</v>
       </c>
       <c r="E9" t="n">
         <v>-0.045</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.026</v>
+        <v>0.0232</v>
       </c>
       <c r="G9" t="n">
         <v>-0.365</v>
@@ -1156,13 +1156,13 @@
         <v>0.3706</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0766</v>
+        <v>-0.0274</v>
       </c>
       <c r="T9" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. CASAS GARCIA</t>
+          <t>T. PERRY II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4095</v>
+        <v>-0.07779999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3834</v>
+        <v>1.5252</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.026</v>
+        <v>-1.603</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8873</v>
+        <v>2.9123</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8873</v>
+        <v>0.1231</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2.7893</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5884</v>
+        <v>4.02</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5884</v>
+        <v>1.2923</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.7277</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2989</v>
+        <v>-1.1077</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2989</v>
+        <v>-1.1693</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.0616</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3706</v>
+        <v>-2.594</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2072</v>
+        <v>-0.3961</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1094</v>
+        <v>-0.0479</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0977</v>
+        <v>-0.3482</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.468</v>
+        <v>-0.1636</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2322</v>
+        <v>0.1319</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7001</v>
+        <v>-0.2956</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5472</v>
+        <v>-0.7536</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1247</v>
+        <v>0.7028</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4225</v>
+        <v>-1.4564</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1183</v>
+        <v>-0.3421</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9109</v>
+        <v>0.8072</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2074</v>
+        <v>-1.1493</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.4115</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7863</v>
+        <v>-0.1044</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2152</v>
+        <v>-0.3071</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1853</v>
+        <v>1.297</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2617</v>
+        <v>-0.7076</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6703</v>
+        <v>-0.1554</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5914</v>
+        <v>-0.5521</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.4621</v>
+        <v>0.0005</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.63</v>
+        <v>0.6294</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8321</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>S. CASAS GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9055</v>
+        <v>-0.3602</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3145</v>
+        <v>-0.3834</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.591</v>
+        <v>0.0232</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7536</v>
+        <v>-0.8873</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7028</v>
+        <v>-0.8873</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4564</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3421</v>
+        <v>-0.5884</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8072</v>
+        <v>-0.5884</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1493</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4115</v>
+        <v>-0.2989</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1044</v>
+        <v>-0.2989</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3071</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.297</v>
+        <v>0.3706</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4495</v>
+        <v>-0.1579</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6019</v>
+        <v>-0.1094</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8476</v>
+        <v>-0.0485</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0005</v>
+        <v>0.3144</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. PERRY II</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9663</v>
+        <v>-1.3215</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8829</v>
+        <v>0.7972</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.8492</v>
+        <v>-2.1187</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9123</v>
+        <v>1.5472</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1231</v>
+        <v>1.1247</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7893</v>
+        <v>0.4225</v>
       </c>
       <c r="J13" t="n">
-        <v>4.02</v>
+        <v>2.1183</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2923</v>
+        <v>1.9109</v>
       </c>
       <c r="L13" t="n">
-        <v>2.7277</v>
+        <v>0.2074</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1077</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1693</v>
+        <v>-0.7863</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0616</v>
+        <v>0.2152</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.594</v>
+        <v>0.1853</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R13" t="n">
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2846</v>
+        <v>0.4082</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6901</v>
+        <v>0.2354</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5944</v>
+        <v>0.1728</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-3.4621</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2589</v>
+        <v>-0.63</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2589</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.0522</v>
+        <v>23.5994</v>
       </c>
       <c r="E14" t="n">
-        <v>32.399</v>
+        <v>32.9462</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.3467</v>
+        <v>-9.3468</v>
       </c>
       <c r="G14" t="n">
         <v>30.3378</v>
@@ -1531,13 +1531,13 @@
         <v>-8.0169</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.788999999999999</v>
+        <v>-6.789</v>
       </c>
       <c r="O14" t="n">
         <v>-1.2276</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9265999999999992</v>
+        <v>0.9265999999999996</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.8964</v>
@@ -1546,19 +1546,19 @@
         <v>14.823</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.5494</v>
+        <v>-2.0021</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6479</v>
+        <v>2.195</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.1971</v>
+        <v>-4.1972</v>
       </c>
       <c r="V14" t="n">
         <v>-5.6627</v>
       </c>
       <c r="W14" t="n">
-        <v>6.2931</v>
+        <v>6.293099999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-11.956</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4031</v>
+        <v>4.9433</v>
       </c>
       <c r="E15" t="n">
-        <v>7.7902</v>
+        <v>6.0275</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3872</v>
+        <v>-1.0843</v>
       </c>
       <c r="G15" t="n">
         <v>4.9688</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2675</v>
+        <v>0.8077</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8689</v>
+        <v>1.1061</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6014</v>
+        <v>-0.2985</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5744</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.778</v>
+        <v>0.9584</v>
       </c>
       <c r="E16" t="n">
-        <v>2.645</v>
+        <v>2.5471</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8671</v>
+        <v>-1.5888</v>
       </c>
       <c r="G16" t="n">
         <v>-1.7922</v>
@@ -1702,13 +1702,13 @@
         <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0525</v>
+        <v>0.2329</v>
       </c>
       <c r="T16" t="n">
-        <v>0.291</v>
+        <v>0.1931</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2385</v>
+        <v>0.0398</v>
       </c>
       <c r="V16" t="n">
         <v>2.5177</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7348</v>
+        <v>0.7589</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5777</v>
+        <v>0.6756</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1572</v>
+        <v>0.0833</v>
       </c>
       <c r="G17" t="n">
         <v>0.4347</v>
@@ -1780,13 +1780,13 @@
         <v>0.1853</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1149</v>
+        <v>0.139</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2243</v>
+        <v>0.1505</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6872</v>
+        <v>-0.1489</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1771</v>
+        <v>0.4104</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5101</v>
+        <v>-0.5593</v>
       </c>
       <c r="G20" t="n">
         <v>-1.699</v>
@@ -2014,13 +2014,13 @@
         <v>1.8529</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8585</v>
+        <v>-0.3202</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.383</v>
+        <v>0.2046</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4755</v>
+        <v>-0.5248</v>
       </c>
       <c r="V20" t="n">
         <v>0.9439</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>D. VIGARIO CONSTANTINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7204</v>
+        <v>-1.8663</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2489</v>
+        <v>-1.7349</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9693</v>
+        <v>-0.1314</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.159</v>
+        <v>-0.1021</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0502</v>
+        <v>-0.3633</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.1087</v>
+        <v>0.2611</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9538</v>
+        <v>0.365</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0783</v>
+        <v>0.365</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1244</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.2051</v>
+        <v>-0.4671</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.972</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.2331</v>
+        <v>0.2611</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1117</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0679</v>
+        <v>0.2369</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9439</v>
+        <v>0.0864</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1241</v>
+        <v>0.1505</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2589</v>
+        <v>-1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2589</v>
+        <v>-1.26</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. VIGARIO CONSTANTINO</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9883</v>
+        <v>-2.1619</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9308</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0575</v>
+        <v>-3.117</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1021</v>
+        <v>-5.159</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3633</v>
+        <v>-2.0502</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2611</v>
+        <v>-3.1087</v>
       </c>
       <c r="J22" t="n">
-        <v>0.365</v>
+        <v>-0.9538</v>
       </c>
       <c r="K22" t="n">
-        <v>0.365</v>
+        <v>-1.0783</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.1244</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4671</v>
+        <v>-4.2051</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.972</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2611</v>
+        <v>-3.2331</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1149</v>
+        <v>0.6264</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1094</v>
+        <v>0.6501</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2243</v>
+        <v>-0.0236</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.26</v>
+        <v>1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>-1.26</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RICARDO</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6585</v>
+        <v>-3.6621</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4459</v>
+        <v>2.5027</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.1043</v>
+        <v>-6.1649</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.7316</v>
+        <v>-3.4118</v>
       </c>
       <c r="H23" t="n">
-        <v>-4.3431</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3885</v>
+        <v>-2.7601</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.155</v>
+        <v>3.723</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.4833</v>
+        <v>2.3746</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3283</v>
+        <v>1.3484</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.5766</v>
+        <v>-7.1348</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8598</v>
+        <v>-3.0262</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.7168</v>
+        <v>-4.1085</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2234</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.6322</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1094</v>
+        <v>-0.3239</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2537</v>
+        <v>0.0031</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3631</v>
+        <v>-0.3271</v>
       </c>
       <c r="V23" t="n">
-        <v>4.406</v>
+        <v>0.6294</v>
       </c>
       <c r="W23" t="n">
-        <v>5.9793</v>
+        <v>0.6294</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.5733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. ANDRADE</t>
+          <t>J. RICARDO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6681</v>
+        <v>-4.1688</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8763</v>
+        <v>0.9355</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7917</v>
+        <v>-5.1043</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.8906</v>
+        <v>-6.7316</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.9229</v>
+        <v>-4.3431</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9676</v>
+        <v>-2.3885</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2942</v>
+        <v>-1.155</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6627</v>
+        <v>-2.4833</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6315</v>
+        <v>1.3283</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.5964</v>
+        <v>-5.5766</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.2603</v>
+        <v>-1.8598</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.3361</v>
+        <v>-3.7168</v>
       </c>
       <c r="P24" t="n">
-        <v>1.297</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R24" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5544</v>
+        <v>0.3802</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4179</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1365</v>
+        <v>-0.3631</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6289</v>
+        <v>4.406</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>5.9793</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6289</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>E. ANDRADE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.9197</v>
+        <v>-4.8811</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5234</v>
+        <v>-2.0722</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.4432</v>
+        <v>-2.8089</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.4118</v>
+        <v>-5.8906</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6516999999999999</v>
+        <v>-3.9229</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.7601</v>
+        <v>-1.9676</v>
       </c>
       <c r="J25" t="n">
-        <v>3.723</v>
+        <v>-2.2942</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3746</v>
+        <v>-1.6627</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3484</v>
+        <v>-0.6315</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.1348</v>
+        <v>-3.5964</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.0262</v>
+        <v>-2.2603</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.1085</v>
+        <v>-1.3361</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5815</v>
+        <v>0.3414</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9762</v>
+        <v>0.222</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6054</v>
+        <v>0.1194</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6294</v>
+        <v>-0.6289</v>
       </c>
       <c r="W25" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.3724</v>
+        <v>-5.7879</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0849</v>
+        <v>-2.3534</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.2875</v>
+        <v>-3.4345</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.2614</v>
+        <v>-4.6379</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.3003</v>
+        <v>-0.8763</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.9611</v>
+        <v>-3.7616</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9156</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.04</v>
+        <v>1.6828</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1244</v>
+        <v>-1.1813</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.3458</v>
+        <v>-5.1394</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.2603</v>
+        <v>-2.5591</v>
       </c>
       <c r="O26" t="n">
-        <v>-4.0855</v>
+        <v>-2.5803</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R26" t="n">
         <v>1.4823</v>
       </c>
       <c r="S26" t="n">
-        <v>1.592</v>
+        <v>0.4446</v>
       </c>
       <c r="T26" t="n">
-        <v>1.7571</v>
+        <v>0.222</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1652</v>
+        <v>0.2226</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2589</v>
+        <v>0.6289</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-6.8977</v>
+        <v>-7.3271</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.3326</v>
+        <v>-1.0642</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.5651</v>
+        <v>-6.2629</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.6379</v>
+        <v>-7.2614</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.8763</v>
+        <v>-3.3003</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.7616</v>
+        <v>-3.9611</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5014999999999999</v>
+        <v>-0.9156</v>
       </c>
       <c r="K27" t="n">
-        <v>1.6828</v>
+        <v>-1.04</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.1813</v>
+        <v>0.1244</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.1394</v>
+        <v>-6.3458</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.5591</v>
+        <v>-2.2603</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.5803</v>
+        <v>-4.0855</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.2234</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R27" t="n">
         <v>1.4823</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.6653</v>
+        <v>0.6373</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7573</v>
+        <v>0.7779</v>
       </c>
       <c r="U27" t="n">
-        <v>0.092</v>
+        <v>-0.1405</v>
       </c>
       <c r="V27" t="n">
-        <v>0.6289</v>
+        <v>-1.2589</v>
       </c>
       <c r="W27" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-23.0522</v>
+        <v>-22.3993</v>
       </c>
       <c r="E28" t="n">
-        <v>7.7736</v>
+        <v>7.773399999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-30.8258</v>
+        <v>-30.173</v>
       </c>
       <c r="G28" t="n">
         <v>-30.3379</v>
@@ -2629,7 +2629,7 @@
         <v>-22.8462</v>
       </c>
       <c r="P28" t="n">
-        <v>-0.9263999999999999</v>
+        <v>-0.9263999999999998</v>
       </c>
       <c r="Q28" t="n">
         <v>-14.8228</v>
@@ -2638,13 +2638,13 @@
         <v>13.8965</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5494</v>
+        <v>3.2023</v>
       </c>
       <c r="T28" t="n">
         <v>4.1972</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.6479</v>
+        <v>-0.9947999999999999</v>
       </c>
       <c r="V28" t="n">
         <v>5.6626</v>
